--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260713.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>13.45%</t>
+          <t>13.80%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>11.97%</t>
+          <t>12.18%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.73%</t>
+          <t>11.85%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>11.32%</t>
+          <t>10.84%</t>
         </is>
       </c>
     </row>
@@ -699,51 +699,51 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,136,010,000</t>
+          <t>1,136,050,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.74%</t>
+          <t>7.55%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>775,490,000</t>
+          <t>34,000,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>4.45%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>34,000,000</t>
+          <t>775,490,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,88 +755,88 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>37,075,000</t>
+          <t>98,903,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>98,903,000</t>
+          <t>1,936</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,400,000</t>
+          <t>37,075,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,872</t>
+          <t>22,560,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -880,95 +880,95 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>11,400,000</t>
+          <t>71,330,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>71,330,000</t>
+          <t>11,400,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>64,710,000</t>
+          <t>209,210,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>209,210,000</t>
+          <t>64,710,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1012,90 +1012,90 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>119,100,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>119,100,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>73,160,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>73,160,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,218,000</t>
+          <t>12,238,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1188,46 +1188,46 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,370,000</t>
+          <t>34,120,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>34,120,000</t>
+          <t>15,370,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,22 +1239,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,330,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>29,940,000</t>
+          <t>13,420,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,44 +1327,44 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>29,940,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1386,24 +1386,24 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>29,006,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,22 +1459,22 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>29,006,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>454,452,395</t>
+          <t>516,964,385</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -1531,10 +1531,28 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,682,349,660</t>
+          <t>1,852,761,332</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>-144,360,767</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
